--- a/data/trans_bre/P1412-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1412-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -634,22 +634,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,13</t>
+          <t>-0,54; 1,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,72</t>
+          <t>-0,8; 0,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,77</t>
+          <t>-0,5; 0,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-83,79; 573,97</t>
+          <t>-75,95; 602,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,61; 255,54</t>
+          <t>-60,71; 272,72</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-35,11%</t>
+          <t>-37,17%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,45</t>
+          <t>-1,27; 0,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,02</t>
+          <t>-1,34; 0,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,3</t>
+          <t>-0,75; 0,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,47; 101,34</t>
+          <t>-83,7; 157,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,96</t>
+          <t>-93,0; 30,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,46; 121,83</t>
+          <t>-81,18; 98,47</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-77,04%</t>
+          <t>-66,62%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,55</t>
+          <t>-0,28; 1,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,45</t>
+          <t>-1,56; 0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; -0,29</t>
+          <t>-1,95; -0,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-52,44; 834,17</t>
+          <t>-49,57; 719,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-88,85; 142,84</t>
+          <t>-90,9; 130,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-96,57; -28,78</t>
+          <t>-92,37; 15,2</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-47,36%</t>
+          <t>-41,04%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,39</t>
+          <t>-0,86; 0,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,89</t>
+          <t>-0,44; 0,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,08</t>
+          <t>-1,31; 0,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,4; 268,21</t>
+          <t>-87,99; 291,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,7; 390,79</t>
+          <t>-64,42; 434,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,4; 17,48</t>
+          <t>-73,38; 22,27</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-43,8%</t>
+          <t>-39,28%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,46</t>
+          <t>-0,4; 0,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,17</t>
+          <t>-0,61; 0,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; -0,03</t>
+          <t>-0,76; -0,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 101,59</t>
+          <t>-45,05; 96,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-64,42; 38,21</t>
+          <t>-63,37; 35,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -2,68</t>
+          <t>-62,68; -3,27</t>
         </is>
       </c>
     </row>
